--- a/tool/kintone-aggregator/clients/template/client.xlsx
+++ b/tool/kintone-aggregator/clients/template/client.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD43AF-7D5C-43BE-813F-151E7C219873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E825E71-29A0-4496-8D29-D44E78989CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
   <sheets>
     <sheet name="受講生一覧" sheetId="3" r:id="rId1"/>

--- a/tool/kintone-aggregator/clients/template/client.xlsx
+++ b/tool/kintone-aggregator/clients/template/client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E825E71-29A0-4496-8D29-D44E78989CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C971EC-659F-4DE3-AA7E-02E0CDA185C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -88,11 +88,40 @@
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>除外日-開始</t>
+    <rPh sb="0" eb="2">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>除外日-終了</t>
+    <rPh sb="0" eb="2">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -725,7 +754,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,6 +762,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1092,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7305DA-9532-48D5-A9AB-D0B7DDD41B28}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="34.69921875" bestFit="1" customWidth="1"/>
@@ -1100,9 +1135,11 @@
     <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.19921875" customWidth="1"/>
     <col min="6" max="6" width="30.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1120,6 +1157,12 @@
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tool/kintone-aggregator/clients/template/client.xlsx
+++ b/tool/kintone-aggregator/clients/template/client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C971EC-659F-4DE3-AA7E-02E0CDA185C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F255EA9A-40CB-443C-A861-A4F0EC72026D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -758,17 +758,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1134,35 +1134,35 @@
     <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.19921875" customWidth="1"/>
-    <col min="6" max="6" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16.296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>10</v>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1182,16 +1182,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
